--- a/backend/data/excel/3d336983f675_data.xlsx
+++ b/backend/data/excel/3d336983f675_data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="메타데이터" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="통계데이터" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="관련용어" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,7 +516,11 @@
           <t>키워드</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>주택/주택건설실적통계(착공)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -537,7 +542,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-08 15:00:02</t>
+          <t>2025-09-11 11:37:29</t>
         </is>
       </c>
     </row>
@@ -552,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:DO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,10 +626,540 @@
           <t>ibsheet_cell_19</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_21</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_23</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_25</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_27</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_29</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_31</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_33</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_35</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_37</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_39</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_41</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_43</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_45</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_47</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_49</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_51</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_53</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_55</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_56</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_57</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_59</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_61</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_63</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_65</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_67</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_69</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_71</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_73</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_75</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_764</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_767</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_769</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_771</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_773</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_775</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_777</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_779</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_781</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_783</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_785</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_787</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_789</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_791</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_793</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_795</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_797</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_799</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_801</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_803</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_805</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_807</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_809</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_811</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_813</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_815</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_817</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_819</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_821</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_1491</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_1492</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_22</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_24</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_28</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_30</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_34</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_36</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_38</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_40</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_44</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_46</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_50</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_52</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_60</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_62</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_66</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_68</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_72</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_74</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_76</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_78</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_79</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_81</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_82</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_84</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_85</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_87</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_88</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_90</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_91</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_93</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_94</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_95</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_97</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_98</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_100</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_101</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_103</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_104</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_705</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_706</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_58</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_77</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_80</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_83</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_837</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>ibsheet_cell_838</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -686,14 +1221,360 @@
           <t>{'value': '전국', 'unit': 'text', 'raw': '전국'}</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{'value': '서울', 'unit': 'text', 'raw': '서울'}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{'value': '인천', 'unit': 'text', 'raw': '인천'}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{'value': '경기', 'unit': 'text', 'raw': '경기'}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{'value': '부산', 'unit': 'text', 'raw': '부산'}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{'value': '대구', 'unit': 'text', 'raw': '대구'}</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>{'value': '광주', 'unit': 'text', 'raw': '광주'}</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{'value': '대전', 'unit': 'text', 'raw': '대전'}</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>{'value': '울산', 'unit': 'text', 'raw': '울산'}</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>{'value': '세종', 'unit': 'text', 'raw': '세종'}</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>{'value': '강원', 'unit': 'text', 'raw': '강원'}</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>{'value': '충북', 'unit': 'text', 'raw': '충북'}</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>{'value': '충남', 'unit': 'text', 'raw': '충남'}</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>{'value': '전북', 'unit': 'text', 'raw': '전북'}</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>{'value': '전남', 'unit': 'text', 'raw': '전남'}</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>{'value': '경북', 'unit': 'text', 'raw': '경북'}</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>{'value': '경남', 'unit': 'text', 'raw': '경남'}</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>{'value': '제주', 'unit': 'text', 'raw': '제주'}</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>{'value': '공공부문', 'unit': 'text', 'raw': '공공부문'}</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>{'value': '소계', 'unit': 'text', 'raw': '소계'}</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>{'value': '전국', 'unit': 'text', 'raw': '전국'}</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>{'value': '서울', 'unit': 'text', 'raw': '서울'}</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>{'value': '인천', 'unit': 'text', 'raw': '인천'}</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>{'value': '경기', 'unit': 'text', 'raw': '경기'}</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>{'value': '부산', 'unit': 'text', 'raw': '부산'}</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>{'value': '대구', 'unit': 'text', 'raw': '대구'}</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>{'value': '광주', 'unit': 'text', 'raw': '광주'}</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>{'value': '대전', 'unit': 'text', 'raw': '대전'}</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>{'value': '울산', 'unit': 'text', 'raw': '울산'}</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>{'value': '세종', 'unit': 'text', 'raw': '세종'}</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>{'value': '21,400\n642\n94\n9,972\n3,130\n396\n11\n-645\n14\n15\n807\n2,647\n182\n1,559\n258\n684\n1,556\n78\n1,055\n0\n0\n81\n1,370\n74\n0\n-652\n0\n0', 'unit': 'text', 'raw': '21,400\n642\n94\n9,972\n3,130\n396\n11\n-645\n14\n15\n807\n2,647\n182\n1,559\n258\n684\n1,556\n78\n1,055\n0\n0\n81\n1,370\n74\n0\n-652\n0\n0'}</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>{'value': 21400, 'unit': 'number', 'raw': '21,400'}</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>{'value': 642, 'unit': 'number', 'raw': '642'}</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>{'value': 94, 'unit': 'number', 'raw': '94'}</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>{'value': 9972, 'unit': 'number', 'raw': '9,972'}</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>{'value': 3130, 'unit': 'number', 'raw': '3,130'}</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>{'value': 396, 'unit': 'number', 'raw': '396'}</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>{'value': 11, 'unit': 'number', 'raw': '11'}</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>{'value': -645, 'unit': 'number', 'raw': '-645'}</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>{'value': 14, 'unit': 'number', 'raw': '14'}</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>{'value': 15, 'unit': 'number', 'raw': '15'}</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>{'value': 807, 'unit': 'number', 'raw': '807'}</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>{'value': 2647, 'unit': 'number', 'raw': '2,647'}</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>{'value': 182, 'unit': 'number', 'raw': '182'}</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>{'value': 1559, 'unit': 'number', 'raw': '1,559'}</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>{'value': 258, 'unit': 'number', 'raw': '258'}</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>{'value': 684, 'unit': 'number', 'raw': '684'}</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>{'value': 1556, 'unit': 'number', 'raw': '1,556'}</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>{'value': 78, 'unit': 'number', 'raw': '78'}</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>{'value': 1055, 'unit': 'number', 'raw': '1,055'}</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>{'value': 0, 'unit': 'number', 'raw': '0'}</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>{'value': 0, 'unit': 'number', 'raw': '0'}</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>{'value': 81, 'unit': 'number', 'raw': '81'}</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>{'value': 1370, 'unit': 'number', 'raw': '1,370'}</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>{'value': 74, 'unit': 'number', 'raw': '74'}</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>{'value': 0, 'unit': 'number', 'raw': '0'}</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>{'value': -652, 'unit': 'number', 'raw': '-652'}</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>{'value': 0, 'unit': 'number', 'raw': '0'}</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>{'value': 0, 'unit': 'number', 'raw': '0'}</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 360]', 'unit': 'text', 'raw': '[28 / 360]'}</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 360]', 'unit': 'text', 'raw': '[28 / 360]'}</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주택건설 착공실적(월계) (201101 ~ 202507)</t>
+          <t>주택규모별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -751,14 +1632,360 @@
           <t>{'value': 21400, 'unit': 'number', 'raw': '21400'}</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>{'value': '40㎡이하', 'unit': 'text', 'raw': '40㎡이하'}</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>{'value': 3433, 'unit': 'number', 'raw': '3433'}</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{'value': '60~85㎡이하', 'unit': 'text', 'raw': '60~85㎡이하'}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>{'value': 3034, 'unit': 'number', 'raw': '3034'}</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>{'value': '135㎡초과', 'unit': 'text', 'raw': '135㎡초과'}</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>{'value': 445, 'unit': 'number', 'raw': '445'}</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>{'value': '40~60㎡이하', 'unit': 'text', 'raw': '40~60㎡이하'}</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>{'value': 6799, 'unit': 'number', 'raw': '6799'}</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>{'value': '85~135㎡이하', 'unit': 'text', 'raw': '85~135㎡이하'}</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>{'value': 257, 'unit': 'number', 'raw': '257'}</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>{'value': '서울', 'unit': 'text', 'raw': '서울'}</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>{'value': 642, 'unit': 'number', 'raw': '642'}</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>{'value': '40㎡이하', 'unit': 'text', 'raw': '40㎡이하'}</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>{'value': 193, 'unit': 'number', 'raw': '193'}</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>{'value': '60~85㎡이하', 'unit': 'text', 'raw': '60~85㎡이하'}</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>{'value': 89, 'unit': 'number', 'raw': '89'}</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>{'value': '135㎡초과', 'unit': 'text', 'raw': '135㎡초과'}</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>{'value': 189, 'unit': 'number', 'raw': '189'}</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>{'value': '40~60㎡이하', 'unit': 'text', 'raw': '40~60㎡이하'}</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>{'value': 13505, 'unit': 'number', 'raw': '13505'}</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>{'value': '85~135㎡이하', 'unit': 'text', 'raw': '85~135㎡이하'}</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>{'value': 1239, 'unit': 'number', 'raw': '1239'}</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>{'value': '수도권소계', 'unit': 'text', 'raw': '수도권소계'}</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>{'value': 10708, 'unit': 'number', 'raw': '10708'}</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>{'value': '40㎡이하', 'unit': 'text', 'raw': '40㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>{'value': 1878, 'unit': 'number', 'raw': '1878'}</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>{'value': '60~85㎡이하', 'unit': 'text', 'raw': '60~85㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>{'value': 1329, 'unit': 'number', 'raw': '1329'}</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>{'value': '135㎡초과', 'unit': 'text', 'raw': '135㎡초과'}</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>{'value': 287, 'unit': 'number', 'raw': '287'}</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>{'value': '40~60㎡이하', 'unit': 'text', 'raw': '40~60㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>{'value': 61, 'unit': 'number', 'raw': '61'}</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>{'value': '85~135㎡이하', 'unit': 'text', 'raw': '85~135㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>{'value': 12, 'unit': 'number', 'raw': '12'}</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>{'value': '인천', 'unit': 'text', 'raw': '인천'}</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>{'value': 94, 'unit': 'number', 'raw': '94'}</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>{'value': '40㎡이하', 'unit': 'text', 'raw': '40㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>{'value': 5, 'unit': 'number', 'raw': '5'}</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>{'value': '40~60㎡이하', 'unit': 'text', 'raw': '40~60㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>{'value': 9, 'unit': 'number', 'raw': '9'}</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>{'value': '60~85㎡이하', 'unit': 'text', 'raw': '60~85㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>{'value': 31, 'unit': 'number', 'raw': '31'}</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>{'value': '85~135㎡이하', 'unit': 'text', 'raw': '85~135㎡이하'}</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>{'value': 12, 'unit': 'number', 'raw': '12'}</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>{'value': '135㎡초과', 'unit': 'text', 'raw': '135㎡초과'}</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>{'value': 37, 'unit': 'number', 'raw': '37'}</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>{'value': '경기', 'unit': 'text', 'raw': '경기'}</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>{'value': 9972, 'unit': 'number', 'raw': '9972'}</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>{'value': '40㎡이하', 'unit': 'text', 'raw': '40㎡이하'}</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>{'value': 153, 'unit': 'number', 'raw': '153'}</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>{'value': '40~60㎡이하', 'unit': 'text', 'raw': '40~60㎡이하'}</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>{'value': 1676, 'unit': 'number', 'raw': '1676'}</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>{'value': '60~85㎡이하', 'unit': 'text', 'raw': '60~85㎡이하'}</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>{'value': 6707, 'unit': 'number', 'raw': '6707'}</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 132]', 'unit': 'text', 'raw': '[28 / 132]'}</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 132]', 'unit': 'text', 'raw': '[28 / 132]'}</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>주택건설 착공실적(월계) (201101 ~ 202507)</t>
+          <t>주택유형별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -816,394 +2043,344 @@
           <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{'value': '다가구', 'unit': 'text', 'raw': '다가구'}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>{'value': '수도권소계', 'unit': 'text', 'raw': '수도권소계'}</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>{'value': '다가구', 'unit': 'text', 'raw': '다가구'}</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>{'value': '서울', 'unit': 'text', 'raw': '서울'}</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>{'value': '다가구', 'unit': 'text', 'raw': '다가구'}</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>{'value': '다세대', 'unit': 'text', 'raw': '다세대'}</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>{'value': '계(다가구가구수기준)', 'unit': 'text', 'raw': '계(다가구가구수기준)'}</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>{'value': '단독', 'unit': 'text', 'raw': '단독'}</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>{'value': '다가구', 'unit': 'text', 'raw': '다가구'}</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>{'value': '연립', 'unit': 'text', 'raw': '연립'}</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>{'value': '아파트', 'unit': 'text', 'raw': '아파트'}</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>{'value': '인천', 'unit': 'text', 'raw': '인천'}</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 176]', 'unit': 'text', 'raw': '[28 / 176]'}</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>{'value': '[28 / 176]', 'unit': 'text', 'raw': '[28 / 176]'}</t>
+        </is>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>주택규모별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 총계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종\n강원\n충북\n충남\n전북\n전남\n경북\n경남\n제주\n공공부문 소계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종', 'unit': 'text', 'raw': '2025-07 총계 총계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종\n강원\n충북\n충남\n전북\n전남\n경북\n경남\n제주\n공공부문 소계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종'}</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>{'value': '전국', 'unit': 'text', 'raw': '전국'}</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>용어</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>정의</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>주택규모별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 계 21400\n40㎡이하 189\n40~60㎡이하 3433\n60~85㎡이하 13505\n85~135㎡이하 3034\n135㎡초과 1239\n수도권소계 계 10708\n40㎡이하 445\n40~60㎡이하 1878\n60~85㎡이하 6799\n85~135㎡이하 1329\n135㎡초과 257\n서울 계 642\n40㎡이하 287\n40~60㎡이하 193\n60~85㎡이하 61\n85~135㎡이하 89\n135㎡초과 12\n인천 계 94\n40㎡이하 5\n40~60㎡이하 9\n60~85㎡이하 31\n85~135㎡이하 12\n135㎡초과 37\n경기 계 9972\n40㎡이하 153\n40~60㎡이하 1676\n60~85㎡이하 6707', 'unit': 'text', 'raw': '2025-07 총계 계 21400\n40㎡이하 189\n40~60㎡이하 3433\n60~85㎡이하 13505\n85~135㎡이하 3034\n135㎡초과 1239\n수도권소계 계 10708\n40㎡이하 445\n40~60㎡이하 1878\n60~85㎡이하 6799\n85~135㎡이하 1329\n135㎡초과 257\n서울 계 642\n40㎡이하 287\n40~60㎡이하 193\n60~85㎡이하 61\n85~135㎡이하 89\n135㎡초과 12\n인천 계 94\n40㎡이하 5\n40~60㎡이하 9\n60~85㎡이하 31\n85~135㎡이하 12\n135㎡초과 37\n경기 계 9972\n40㎡이하 153\n40~60㎡이하 1676\n60~85㎡이하 6707'}</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>{'value': 21400, 'unit': 'number', 'raw': '21400'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>주택규모별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n수도권소계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n서울 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n인천 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구', 'unit': 'text', 'raw': '2025-07 총계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n수도권소계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n서울 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n인천 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구'}</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>주택유형별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 총계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종\n강원\n충북\n충남\n전북\n전남\n경북\n경남\n제주\n공공부문 소계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종', 'unit': 'text', 'raw': '2025-07 총계 총계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종\n강원\n충북\n충남\n전북\n전남\n경북\n경남\n제주\n공공부문 소계 전국\n서울\n인천\n경기\n부산\n대구\n광주\n대전\n울산\n세종'}</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>{'value': '전국', 'unit': 'text', 'raw': '전국'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>주택유형별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 계 21400\n40㎡이하 189\n40~60㎡이하 3433\n60~85㎡이하 13505\n85~135㎡이하 3034\n135㎡초과 1239\n수도권소계 계 10708\n40㎡이하 445\n40~60㎡이하 1878\n60~85㎡이하 6799\n85~135㎡이하 1329\n135㎡초과 257\n서울 계 642\n40㎡이하 287\n40~60㎡이하 193\n60~85㎡이하 61\n85~135㎡이하 89\n135㎡초과 12\n인천 계 94\n40㎡이하 5\n40~60㎡이하 9\n60~85㎡이하 31\n85~135㎡이하 12\n135㎡초과 37\n경기 계 9972\n40㎡이하 153\n40~60㎡이하 1676\n60~85㎡이하 6707', 'unit': 'text', 'raw': '2025-07 총계 계 21400\n40㎡이하 189\n40~60㎡이하 3433\n60~85㎡이하 13505\n85~135㎡이하 3034\n135㎡초과 1239\n수도권소계 계 10708\n40㎡이하 445\n40~60㎡이하 1878\n60~85㎡이하 6799\n85~135㎡이하 1329\n135㎡초과 257\n서울 계 642\n40㎡이하 287\n40~60㎡이하 193\n60~85㎡이하 61\n85~135㎡이하 89\n135㎡초과 12\n인천 계 94\n40㎡이하 5\n40~60㎡이하 9\n60~85㎡이하 31\n85~135㎡이하 12\n135㎡초과 37\n경기 계 9972\n40㎡이하 153\n40~60㎡이하 1676\n60~85㎡이하 6707'}</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>{'value': '계', 'unit': 'text', 'raw': '계'}</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>{'value': 21400, 'unit': 'number', 'raw': '21400'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>주택유형별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'value': '월(Monthly)', 'unit': 'text', 'raw': '월(Monthly)'}</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'value': '구  분', 'unit': 'text', 'raw': '구  분'}</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>{'value': '부문명', 'unit': 'text', 'raw': '부문명'}</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>{'value': '시도별', 'unit': 'text', 'raw': '시도별'}</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>{'value': '착공실적', 'unit': 'text', 'raw': '착공실적'}</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07 총계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n수도권소계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n서울 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n인천 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구', 'unit': 'text', 'raw': '2025-07 총계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n수도권소계 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n서울 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구\n다세대 다세대\n연립 연립\n아파트 아파트\n인천 계(다가구동수기준) 계(다가구동수기준)\n계(다가구가구수기준) 계(다가구가구수기준)\n단독 단독\n다가구'}</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{'value': '2025-07', 'unit': 'text', 'raw': '2025-07'}</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>{'value': '총계', 'unit': 'text', 'raw': '총계'}</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>{'value': '계(다가구동수기준)', 'unit': 'text', 'raw': '계(다가구동수기준)'}</t>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>주택/주택건설실적통계(착공)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>주택정책과 (곽경래, ☏ 0442013336)</t>
         </is>
       </c>
     </row>

--- a/backend/data/excel/3d336983f675_data.xlsx
+++ b/backend/data/excel/3d336983f675_data.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-11 11:37:29</t>
+          <t>2025-09-16 10:40:53</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>주택건설 착공실적(월계) (201101 ~ 202507)</t>
+          <t>기본 통계표</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주택규모별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
+          <t>기본 통계표</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>주택유형별 주택건설 착공실적(월계) (201101 ~ 202507)</t>
+          <t>기본 통계표</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/backend/data/excel/3d336983f675_data.xlsx
+++ b/backend/data/excel/3d336983f675_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,201 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-21 22:48:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)대상</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>○ 건축법 제11조의 건축허가 대상 주택 ○ 건축법 제14조의 건축신고 대상 주택 ○ 주택법 제15조의 주택건설사업 사업계획승인 대상 주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)근거</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>○ 승인번호 제116026호(승인일자 2002-04-03) ○ 주택건설실적(분양) 승인 통계 변경(변경승인일자 2020-12-30)
-○ 통계법 제18조 규정에 의한 승인통계지정, 통계법 제27조 규정에 의한 통계공표.
-○ 건축법 제11조 건축법 제14조 주택법 제15조</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)목적</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>주택정책 수립 관련 정책자료 활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>통계정보/공표주기</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>익월말</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>통계정보/공표방법</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>「국토교통통계연보」, 보도자료, 국토교통통계누리(http://stat.molit.go.kr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>통계정보/주석</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1) 주)(-)수치는 취소 등의 사유로 정정 과정에서 발생
-자료 : 국토교통부 주택토지실 주택정책관 주택정책과
-2) 2023년(1~12월) 주택건설((인허가, 착공, 준공) 실적 수정 공표(2024.4.30.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>메인페이지/검색분야</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>주택/주택건설실적통계(착공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>메인페이지/담당부서</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>주택정책과 (정용욱, ☏ 0442014148)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>관련용어/주요항목</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>단독(다가구)는 동수 기준임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>관련용어/의미분석</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>관련용어
-등록된 관련 용어가 없습니다.
-승인통계는 로 표시됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>관련용어/관련용어</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>등록된 관련 용어가 없습니다.
-승인통계는 로 표시됩니다.</t>
+          <t>2025-09-21 23:02:03</t>
         </is>
       </c>
     </row>
